--- a/artfynd/A 54332-2021 artfynd.xlsx
+++ b/artfynd/A 54332-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54332-2021 artfynd.xlsx
+++ b/artfynd/A 54332-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55195906</v>
+        <v>133006630</v>
       </c>
       <c r="B2" t="n">
-        <v>88937</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256756</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uskavi, Silvergruvorna, Vstm</t>
+          <t>Falberggruvan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503128.1935685169</v>
+        <v>503260</v>
       </c>
       <c r="R2" t="n">
-        <v>6610385.034402826</v>
+        <v>6610519</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>sporer 9 x 5 µm</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Bengt Jalsborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann, Berit Ragné</t>
+          <t>Bengt Jalsborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105554636</v>
+        <v>71053374</v>
       </c>
       <c r="B3" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,19 +832,29 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:20B Falberggruvan, Vstm</t>
+          <t>Natorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503142.3318165777</v>
+        <v>503273</v>
       </c>
       <c r="R3" t="n">
-        <v>6610441.183941514</v>
+        <v>6610386</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,27 +878,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5 m upp. Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>1-2 kolonier på ung ask</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,31 +918,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Jonas Örnborg, Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105554637</v>
+        <v>105554631</v>
       </c>
       <c r="B4" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,17 +958,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:20A Falberggruvan, Vstm</t>
+          <t>Natorpsområdet Yta 7:4 Falberggruvan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503203.1057998639</v>
+        <v>503280</v>
       </c>
       <c r="R4" t="n">
-        <v>6610463.99371715</v>
+        <v>6610439</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,34 +1007,39 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1058,15 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105554642</v>
+        <v>105554636</v>
       </c>
       <c r="B5" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,17 +1088,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:19 Falberggruvan, Vstm</t>
+          <t>Natorpsområdet Yta 7:20B Falberggruvan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503236.5612240188</v>
+        <v>503143</v>
       </c>
       <c r="R5" t="n">
-        <v>6610441.769932062</v>
+        <v>6610441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,34 +1137,39 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>5 m upp. Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1179,15 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120766114</v>
+        <v>113473534</v>
       </c>
       <c r="B6" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1228,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:19 Falberggruvan, Vstm</t>
+          <t>Natorpsområdet Yta 7:20B Falberggruvan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503252</v>
+        <v>503230</v>
       </c>
       <c r="R6" t="n">
-        <v>6610418</v>
+        <v>6610514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,12 +1264,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kolonin belägen ca 4 m över marken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,14 +1309,484 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113548216</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långbansgruvan vägskäl, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>503254</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6610523</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1994-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1994-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120766114</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Natorpsområdet Yta 7:19 Falberggruvan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>503252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6610418</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133006619</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Falberggruvan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>503260</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6610519</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>55195906</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Uskavi, Silvergruvorna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>503128</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6610385</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sporer 9 x 5 µm</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann, Berit Ragné</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54332-2021 artfynd.xlsx
+++ b/artfynd/A 54332-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133006630</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71053374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,6 +1072,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1187,6 +1207,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473534</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1432,6 +1462,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113548216</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1562,6 +1597,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1685,6 +1725,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133006619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1787,8 +1832,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55195906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>